--- a/gfx_infant_spot_kids_gap.xlsx
+++ b/gfx_infant_spot_kids_gap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zacknewman/Documents/ZackNewsMan, LLC/Colorado Sun/Child care/Data - child care/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{BA49772C-D013-6E4D-8C25-9B4D7F4BFA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{111201C2-6020-974E-8076-2AD160D82D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1820" windowWidth="27240" windowHeight="16440"/>
   </bookViews>
@@ -16,7 +16,19 @@
     <sheet name="for gfx" sheetId="2" r:id="rId1"/>
     <sheet name="infant_spot_kids_gap" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
